--- a/TextGame project/Assets/Resources/Story/7.xlsx
+++ b/TextGame project/Assets/Resources/Story/7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762C52B0-10BC-4726-99D8-25343F59FB52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94A4C171-87A7-4A90-A75B-571E386C6F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -806,7 +806,7 @@
         <v>7</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>32</v>
@@ -832,7 +832,7 @@
         <v>7</v>
       </c>
       <c r="S3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T3" s="1">
         <v>-640.83010000000002</v>
@@ -852,7 +852,7 @@
         <v>7</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T4" s="1">
         <v>-640.83010000000002</v>
@@ -872,7 +872,7 @@
         <v>7</v>
       </c>
       <c r="S5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T5" s="1">
         <v>-640.83010000000002</v>
@@ -892,7 +892,7 @@
         <v>7</v>
       </c>
       <c r="S6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T6" s="1">
         <v>-640.83010000000002</v>
@@ -912,7 +912,7 @@
         <v>7</v>
       </c>
       <c r="S7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T7" s="1">
         <v>-640.83010000000002</v>
@@ -932,7 +932,7 @@
         <v>7</v>
       </c>
       <c r="S8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T8" s="1">
         <v>-640.83010000000002</v>
@@ -952,7 +952,7 @@
         <v>7</v>
       </c>
       <c r="S9">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T9" s="1">
         <v>-640.83010000000002</v>
@@ -972,7 +972,7 @@
         <v>7</v>
       </c>
       <c r="S10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T10" s="1">
         <v>-640.83010000000002</v>
@@ -992,7 +992,7 @@
         <v>7</v>
       </c>
       <c r="S11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T11" s="1">
         <v>-640.83010000000002</v>
